--- a/sample-data/projects.xlsx
+++ b/sample-data/projects.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Projects" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,247 +422,189 @@
         <v>Supervisor</v>
       </c>
       <c r="H1" t="str">
+        <v>Supervisor_email</v>
+      </c>
+      <c r="I1" t="str">
         <v>Cosupervisor</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Supervisor_email</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Machine Learning</v>
+        <v>Signal Processing</v>
       </c>
       <c r="B2" t="str">
-        <v>ML-001</v>
+        <v>SP-101</v>
       </c>
       <c r="C2" t="str">
-        <v>Deep Learning for Medical Image Analysis</v>
+        <v>Adaptive Noise Cancellation using Deep Learning</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2" t="str">
-        <v>Implementation and testing of CNN models for detecting diseases from X-ray images</v>
+        <v>Simulation + Implementation</v>
       </c>
       <c r="F2" t="str">
-        <v>Prior experience with PyTorch/TensorFlow preferred</v>
+        <v>Background in DSP preferred</v>
       </c>
       <c r="G2" t="str">
-        <v>Dr. Rajesh Kumar</v>
+        <v>Dr. Test Professor</v>
       </c>
       <c r="H2" t="str">
+        <v>test.prof@iiti.ac.in</v>
+      </c>
+      <c r="I2" t="str">
         <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>rajesh.kumar@iiti.ac.in</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Machine Learning</v>
+        <v>Power Systems</v>
       </c>
       <c r="B3" t="str">
-        <v>ML-002</v>
+        <v>PS-201</v>
       </c>
       <c r="C3" t="str">
-        <v>Natural Language Processing for Sentiment Analysis</v>
+        <v>Optimal Placement of EV Charging Stations</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
-        <v>Building NLP models for analyzing customer reviews</v>
+        <v>Simulation</v>
       </c>
       <c r="F3" t="str">
-        <v>Knowledge of transformers and BERT is a plus</v>
+        <v>Knowledge of optimization techniques required</v>
       </c>
       <c r="G3" t="str">
-        <v>Dr. Rajesh Kumar</v>
+        <v>Dr. Test Professor</v>
       </c>
       <c r="H3" t="str">
-        <v>Dr. Priya Sharma</v>
+        <v>test.prof@iiti.ac.in</v>
       </c>
       <c r="I3" t="str">
-        <v>rajesh.kumar@iiti.ac.in</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Power Systems</v>
+        <v>VLSI Design</v>
       </c>
       <c r="B4" t="str">
-        <v>PS-001</v>
+        <v>VL-301</v>
       </c>
       <c r="C4" t="str">
-        <v>Smart Grid Optimization using AI</v>
+        <v>Low Power SRAM Design for IoT Applications</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="str">
-        <v>Developing algorithms for optimal power distribution in smart grids</v>
+        <v>Design + Simulation</v>
       </c>
       <c r="F4" t="str">
-        <v>Strong background in power systems required</v>
+        <v>Cadence Virtuoso experience is a plus</v>
       </c>
       <c r="G4" t="str">
-        <v>Dr. Priya Sharma</v>
+        <v>Dr. Test Professor</v>
       </c>
       <c r="H4" t="str">
+        <v>test.prof@iiti.ac.in</v>
+      </c>
+      <c r="I4" t="str">
         <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>priya.sharma@iiti.ac.in</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>VLSI Design</v>
+        <v>Communication Systems</v>
       </c>
       <c r="B5" t="str">
-        <v>VLSI-001</v>
+        <v>CS-401</v>
       </c>
       <c r="C5" t="str">
-        <v>Low Power SRAM Design</v>
+        <v>MIMO Channel Estimation using Compressed Sensing</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="str">
-        <v>Design and simulation of low-power SRAM cells using Cadence tools</v>
+        <v>Theoretical + Simulation</v>
       </c>
       <c r="F5" t="str">
-        <v>Experience with Cadence Virtuoso required</v>
+        <v>Strong math background needed</v>
       </c>
       <c r="G5" t="str">
-        <v>Dr. Amit Verma</v>
+        <v>Dr. Test Professor</v>
       </c>
       <c r="H5" t="str">
+        <v>test.prof@iiti.ac.in</v>
+      </c>
+      <c r="I5" t="str">
         <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>amit.verma@iiti.ac.in</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>VLSI Design</v>
+        <v>Embedded Systems</v>
       </c>
       <c r="B6" t="str">
-        <v>VLSI-002</v>
+        <v>ES-501</v>
       </c>
       <c r="C6" t="str">
-        <v>FPGA Implementation of Signal Processing Algorithms</v>
+        <v>FPGA-based Real-time Object Detection System</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="str">
-        <v>Implementing DSP algorithms on FPGA using Verilog/VHDL</v>
+        <v>Hardware + Software</v>
       </c>
       <c r="F6" t="str">
-        <v>Knowledge of digital signal processing required</v>
+        <v>Verilog/VHDL knowledge required</v>
       </c>
       <c r="G6" t="str">
-        <v>Dr. Amit Verma</v>
+        <v>Dr. Test Professor</v>
       </c>
       <c r="H6" t="str">
-        <v>Dr. Sunita Patel</v>
+        <v>test.prof@iiti.ac.in</v>
       </c>
       <c r="I6" t="str">
-        <v>amit.verma@iiti.ac.in</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Control Systems</v>
+        <v>Machine Learning</v>
       </c>
       <c r="B7" t="str">
-        <v>CS-001</v>
+        <v>ML-601</v>
       </c>
       <c r="C7" t="str">
-        <v>Autonomous Vehicle Path Planning</v>
+        <v>Federated Learning for Smart Grid Data Privacy</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="str">
-        <v>Developing path planning algorithms for autonomous vehicles</v>
+        <v>Implementation</v>
       </c>
       <c r="F7" t="str">
-        <v>Programming skills in Python/C++ required</v>
+        <v>Python and PyTorch experience preferred</v>
       </c>
       <c r="G7" t="str">
-        <v>Dr. Sunita Patel</v>
+        <v>Dr. Test Professor</v>
       </c>
       <c r="H7" t="str">
+        <v>test.prof@iiti.ac.in</v>
+      </c>
+      <c r="I7" t="str">
         <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>sunita.patel@iiti.ac.in</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Communication Systems</v>
-      </c>
-      <c r="B8" t="str">
-        <v>COM-001</v>
-      </c>
-      <c r="C8" t="str">
-        <v>5G Network Simulation and Analysis</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Simulation of 5G networks using MATLAB/NS3</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Good understanding of wireless communication required</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Dr. Vikram Singh</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>vikram.singh@iiti.ac.in</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Communication Systems</v>
-      </c>
-      <c r="B9" t="str">
-        <v>COM-002</v>
-      </c>
-      <c r="C9" t="str">
-        <v>IoT Security Framework Development</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Designing security protocols for IoT devices</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Interest in cybersecurity is preferred</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Dr. Vikram Singh</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Dr. Rajesh Kumar</v>
-      </c>
-      <c r="I9" t="str">
-        <v>vikram.singh@iiti.ac.in</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
   </ignoredErrors>
 </worksheet>
 </file>